--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R4" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131260583</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1052,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488834</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665228</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488834</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665228</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1253,7 @@
         <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91833</v>
+        <v>57881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1590,7 @@
         <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,23 +2173,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R15" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2238,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,19 +2281,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>81230</v>
+        <v>81231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>131255108</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B35" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,19 +4414,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4434,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R35" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,12 +4483,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,34 +4526,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4581,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,12 +4600,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4623,10 +4632,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B37" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4634,39 +4643,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>57881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>81231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81231</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,23 +4414,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4438,10 +4434,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R35" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4473,7 +4469,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,12 +4479,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4526,39 +4522,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4590,7 +4581,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4600,12 +4591,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4632,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>57881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4643,30 +4634,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R37" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +1027,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1127,7 @@
         <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,30 +1252,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>91836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1590,7 @@
         <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>131260641</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>81231</v>
+        <v>81233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257642</v>
+        <v>131257045</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488913</v>
+        <v>488760</v>
       </c>
       <c r="R23" t="n">
-        <v>6665191</v>
+        <v>6665302</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257045</v>
+        <v>131257642</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488760</v>
+        <v>488913</v>
       </c>
       <c r="R24" t="n">
-        <v>6665302</v>
+        <v>6665191</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>131255108</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131256603</v>
+        <v>131257913</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488625</v>
+        <v>488913</v>
       </c>
       <c r="R33" t="n">
-        <v>6665252</v>
+        <v>6665358</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257913</v>
+        <v>131256603</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488913</v>
+        <v>488625</v>
       </c>
       <c r="R34" t="n">
-        <v>6665358</v>
+        <v>6665252</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,7 +4406,7 @@
         <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131257731</v>
+        <v>131257440</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488874</v>
+        <v>488885</v>
       </c>
       <c r="R38" t="n">
-        <v>6665272</v>
+        <v>6665181</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4852,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257440</v>
+        <v>131257731</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488885</v>
+        <v>488874</v>
       </c>
       <c r="R39" t="n">
-        <v>6665181</v>
+        <v>6665272</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4967,7 +4967,7 @@
         <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256730</v>
+        <v>131256673</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,34 +1598,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488689</v>
+        <v>488652</v>
       </c>
       <c r="R10" t="n">
-        <v>6665231</v>
+        <v>6665282</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131260641</v>
+        <v>131257520</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,39 +1827,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488859</v>
+        <v>488939</v>
       </c>
       <c r="R12" t="n">
-        <v>6665292</v>
+        <v>6665149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257290</v>
+        <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488842</v>
+        <v>488859</v>
       </c>
       <c r="R13" t="n">
-        <v>6665224</v>
+        <v>6665292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256673</v>
+        <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488652</v>
+        <v>488842</v>
       </c>
       <c r="R14" t="n">
-        <v>6665282</v>
+        <v>6665224</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,19 +2173,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R15" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2354,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,23 +2397,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488908</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665154</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>81233</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>81234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257045</v>
+        <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488760</v>
+        <v>488913</v>
       </c>
       <c r="R23" t="n">
-        <v>6665302</v>
+        <v>6665191</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257642</v>
+        <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488913</v>
+        <v>488760</v>
       </c>
       <c r="R24" t="n">
-        <v>6665191</v>
+        <v>6665302</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>131255108</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131257913</v>
+        <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488913</v>
+        <v>488625</v>
       </c>
       <c r="R33" t="n">
-        <v>6665358</v>
+        <v>6665252</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131256603</v>
+        <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488625</v>
+        <v>488913</v>
       </c>
       <c r="R34" t="n">
-        <v>6665252</v>
+        <v>6665358</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B35" t="n">
-        <v>91836</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,30 +4414,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R35" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4469,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,12 +4488,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4520,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,23 +4531,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4581,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,12 +4596,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4623,10 +4628,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4634,39 +4639,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131257440</v>
+        <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488885</v>
+        <v>488874</v>
       </c>
       <c r="R38" t="n">
-        <v>6665181</v>
+        <v>6665272</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4852,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257731</v>
+        <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488874</v>
+        <v>488885</v>
       </c>
       <c r="R39" t="n">
-        <v>6665272</v>
+        <v>6665181</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4967,7 +4967,7 @@
         <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,30 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1241,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,39 +1261,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R10" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1774,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,34 +1832,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R12" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,12 +1906,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,39 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,39 +2061,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,23 +2173,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R15" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2238,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,7 +2270,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
         <v>79249</v>
@@ -2309,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2344,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131257479</v>
+        <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,19 +2393,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488908</v>
+        <v>488704</v>
       </c>
       <c r="R17" t="n">
-        <v>6665154</v>
+        <v>6665241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>81234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81234</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,39 +4414,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R35" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4478,7 +4473,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,12 +4483,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4628,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4639,34 +4634,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,34 +4975,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R40" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,12 +5049,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,39 +5092,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,23 +915,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R4" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +980,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +1023,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1250,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,30 +1252,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,39 +1598,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R10" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,39 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R11" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,34 +1939,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R13" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,12 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,34 +2056,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R14" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>81234</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>81234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,23 +4414,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4438,10 +4434,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R35" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4473,7 +4469,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,12 +4479,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4526,19 +4522,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,39 +4975,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R40" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5049,12 +5044,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5092,34 +5087,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,30 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R4" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131260583</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488834</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665228</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,39 +1261,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1361,7 @@
         <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,34 +1598,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R10" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1824,7 @@
         <v>131256673</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,39 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R13" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,39 +2061,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R14" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,19 +2173,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R15" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,23 +2285,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>81235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81234</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,34 +3849,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R30" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3908,7 +3913,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,12 +3923,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R31" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,12 +4035,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,34 +4975,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R40" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,12 +5049,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,39 +5092,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R4" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +1027,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,34 +1135,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1209,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,30 +1252,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,39 +1598,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R10" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,39 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R11" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R12" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,12 +1896,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,34 +1939,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R13" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,12 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,34 +2056,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R14" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,39 +3849,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R30" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,12 +3918,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,7 +3950,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B31" t="n">
         <v>79250</v>
@@ -3990,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R31" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,34 +4073,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R4" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,30 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,39 +1261,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R7" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>131256691</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131260583</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,34 +1598,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R10" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R12" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,12 +1906,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,39 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R13" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256673</v>
+        <v>131257520</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,39 +2061,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488652</v>
+        <v>488939</v>
       </c>
       <c r="R14" t="n">
-        <v>6665282</v>
+        <v>6665149</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
         <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>81235</v>
+        <v>81238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131255910</v>
+        <v>131257239</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,34 +3508,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488763</v>
+        <v>488852</v>
       </c>
       <c r="R27" t="n">
-        <v>6665157</v>
+        <v>6665286</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3582,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131258531</v>
+        <v>131255910</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488725</v>
+        <v>488763</v>
       </c>
       <c r="R28" t="n">
-        <v>6665212</v>
+        <v>6665157</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,12 +3694,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,39 +3737,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R29" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,34 +3849,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R30" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3908,7 +3913,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,12 +3923,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R31" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,12 +4035,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,39 +4975,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R40" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5049,12 +5044,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5092,34 +5087,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>131256691</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131260583</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131260641</v>
+        <v>131257520</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,39 +1598,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488859</v>
+        <v>488939</v>
       </c>
       <c r="R10" t="n">
-        <v>6665292</v>
+        <v>6665149</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,39 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R11" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R12" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,12 +1896,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,34 +1939,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R13" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,12 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,34 +2056,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R14" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
         <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>81238</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>81239</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131257239</v>
+        <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,39 +3508,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488852</v>
+        <v>488763</v>
       </c>
       <c r="R27" t="n">
-        <v>6665286</v>
+        <v>6665157</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,12 +3577,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131255910</v>
+        <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3649,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488763</v>
+        <v>488725</v>
       </c>
       <c r="R28" t="n">
-        <v>6665157</v>
+        <v>6665212</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,12 +3689,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3737,34 +3732,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R29" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,39 +3849,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R30" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,12 +3918,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3990,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R31" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,34 +4073,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,34 +4975,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R40" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,12 +5049,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,39 +5092,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131256691</v>
+        <v>131255793</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488667</v>
+        <v>488817</v>
       </c>
       <c r="R4" t="n">
-        <v>6665262</v>
+        <v>6665110</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +980,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +1023,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,34 +1135,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1209,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255793</v>
+        <v>131260583</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,30 +1252,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488817</v>
+        <v>488834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665110</v>
+        <v>6665228</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131257520</v>
+        <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488939</v>
+        <v>488689</v>
       </c>
       <c r="R10" t="n">
-        <v>6665149</v>
+        <v>6665231</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131256730</v>
+        <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488689</v>
+        <v>488939</v>
       </c>
       <c r="R11" t="n">
-        <v>6665231</v>
+        <v>6665149</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1814,7 @@
         <v>131260641</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>81245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81239</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,34 +3849,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R30" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3908,7 +3913,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,12 +3923,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R31" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,12 +4035,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B32" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,39 +4975,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R40" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5049,12 +5044,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5092,34 +5087,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131255793</v>
+        <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,19 +915,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488817</v>
+        <v>488876</v>
       </c>
       <c r="R4" t="n">
-        <v>6665110</v>
+        <v>6665177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,23 +1027,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,39 +3849,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R30" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,12 +3918,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,7 +3950,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B31" t="n">
         <v>79260</v>
@@ -3990,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R31" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,34 +4073,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,30 +4414,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R35" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4469,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,12 +4488,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4520,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,23 +4531,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4581,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,12 +4596,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4623,10 +4628,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4634,39 +4639,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,39 +4414,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R35" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4478,7 +4469,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,12 +4479,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4520,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4531,19 +4522,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,7 +4581,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,12 +4591,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4623,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4639,34 +4634,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,23 +915,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R4" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +980,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131257424</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,19 +1023,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488876</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665177</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,23 +2173,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R15" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2238,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131256750</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,19 +2281,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488704</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2382,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B17" t="n">
         <v>79260</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B18" t="n">
         <v>79260</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R18" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B19" t="n">
         <v>79260</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R19" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>81245</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>81245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,7 +3161,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257045</v>
+        <v>131257650</v>
       </c>
       <c r="B24" t="n">
         <v>79260</v>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488760</v>
+        <v>488911</v>
       </c>
       <c r="R24" t="n">
-        <v>6665302</v>
+        <v>6665227</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,7 +3273,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257650</v>
+        <v>131257045</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488911</v>
+        <v>488760</v>
       </c>
       <c r="R25" t="n">
-        <v>6665227</v>
+        <v>6665302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257385</v>
+        <v>131260531</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,19 +4414,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4434,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488876</v>
+        <v>488786</v>
       </c>
       <c r="R35" t="n">
-        <v>6665194</v>
+        <v>6665188</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,12 +4483,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131260531</v>
+        <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,23 +4526,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488786</v>
+        <v>488876</v>
       </c>
       <c r="R36" t="n">
-        <v>6665188</v>
+        <v>6665194</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>131255793</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,34 +1023,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R5" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,7 +1160,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1164,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,39 +1257,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R7" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1590,7 @@
         <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>131260641</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131256750</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488704</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665241</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R17" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R18" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R19" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>81246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81245</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257650</v>
+        <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488911</v>
+        <v>488760</v>
       </c>
       <c r="R24" t="n">
-        <v>6665227</v>
+        <v>6665302</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257045</v>
+        <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488760</v>
+        <v>488911</v>
       </c>
       <c r="R25" t="n">
-        <v>6665302</v>
+        <v>6665227</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>131258531</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258537</v>
+        <v>131257659</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,34 +3849,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488726</v>
+        <v>488901</v>
       </c>
       <c r="R30" t="n">
-        <v>6665209</v>
+        <v>6665222</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3908,7 +3913,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,12 +3923,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,10 +3990,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R31" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4020,7 +4025,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,12 +4035,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131255108</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,39 +4078,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488978</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665417</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131260531</v>
+        <v>131256459</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,34 +4414,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488786</v>
+        <v>488669</v>
       </c>
       <c r="R35" t="n">
-        <v>6665188</v>
+        <v>6665268</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4473,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4483,12 +4488,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,7 +4523,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,10 +4628,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131256459</v>
+        <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4634,39 +4639,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488669</v>
+        <v>488786</v>
       </c>
       <c r="R37" t="n">
-        <v>6665268</v>
+        <v>6665188</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131257487</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131257646</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B4" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,30 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R4" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R5" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R6" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131257424</v>
+        <v>131255793</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,23 +1261,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488876</v>
+        <v>488817</v>
       </c>
       <c r="R7" t="n">
-        <v>6665177</v>
+        <v>6665110</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,33 +1369,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,51 +1490,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,34 +1598,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R10" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R12" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,12 +1906,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257290</v>
+        <v>131256730</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,39 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488842</v>
+        <v>488689</v>
       </c>
       <c r="R13" t="n">
-        <v>6665224</v>
+        <v>6665231</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256673</v>
+        <v>131257520</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,39 +2061,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488652</v>
+        <v>488939</v>
       </c>
       <c r="R14" t="n">
-        <v>6665282</v>
+        <v>6665149</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>91849</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,19 +2173,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R15" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,23 +2285,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,7 +2385,7 @@
         <v>131256750</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>131256401</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>131256403</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>131257637</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B21" t="n">
-        <v>81246</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>81249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,12 +3022,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
         <v>131257642</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>131257045</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>131257650</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131257544</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131255910</v>
+        <v>131257239</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,34 +3508,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488763</v>
+        <v>488852</v>
       </c>
       <c r="R27" t="n">
-        <v>6665157</v>
+        <v>6665286</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3582,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,10 +3614,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131258531</v>
+        <v>131255910</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488725</v>
+        <v>488763</v>
       </c>
       <c r="R28" t="n">
-        <v>6665212</v>
+        <v>6665157</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,12 +3694,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,39 +3737,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R29" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,10 +3838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131257659</v>
+        <v>131258537</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,39 +3849,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488901</v>
+        <v>488726</v>
       </c>
       <c r="R30" t="n">
-        <v>6665222</v>
+        <v>6665209</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,12 +3918,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3950,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B31" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3990,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R31" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131255108</v>
+        <v>131257659</v>
       </c>
       <c r="B32" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,34 +4073,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488978</v>
+        <v>488901</v>
       </c>
       <c r="R32" t="n">
-        <v>6665417</v>
+        <v>6665222</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
         <v>131256603</v>
       </c>
       <c r="B33" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>131257913</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>131256459</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>131257385</v>
       </c>
       <c r="B36" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>131260531</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>131257731</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>131257440</v>
       </c>
       <c r="B39" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,34 +4975,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R40" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,12 +5049,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,39 +5092,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R41" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,7 +5196,7 @@
         <v>131273946</v>
       </c>
       <c r="B42" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>131273991</v>
       </c>
       <c r="B43" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>131256516</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131273940</v>
       </c>
       <c r="B45" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B4" t="n">
         <v>57902</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R4" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131260583</v>
+        <v>131255793</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +1032,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488834</v>
+        <v>488817</v>
       </c>
       <c r="R5" t="n">
-        <v>6665228</v>
+        <v>6665110</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1097,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1250,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255793</v>
+        <v>131256691</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,30 +1252,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488817</v>
+        <v>488667</v>
       </c>
       <c r="R7" t="n">
-        <v>6665110</v>
+        <v>6665262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131260641</v>
+        <v>131256730</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,39 +1598,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488859</v>
+        <v>488689</v>
       </c>
       <c r="R10" t="n">
-        <v>6665292</v>
+        <v>6665231</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1667,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,39 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R11" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256673</v>
+        <v>131260641</v>
       </c>
       <c r="B12" t="n">
         <v>57902</v>
@@ -1861,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488652</v>
+        <v>488859</v>
       </c>
       <c r="R12" t="n">
-        <v>6665282</v>
+        <v>6665292</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,12 +1896,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131256730</v>
+        <v>131257290</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,34 +1939,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488689</v>
+        <v>488842</v>
       </c>
       <c r="R13" t="n">
-        <v>6665231</v>
+        <v>6665224</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,12 +2013,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131257520</v>
+        <v>131256673</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,34 +2056,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488939</v>
+        <v>488652</v>
       </c>
       <c r="R14" t="n">
-        <v>6665149</v>
+        <v>6665282</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131255096</v>
+        <v>131257479</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,23 +2173,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488961</v>
+        <v>488908</v>
       </c>
       <c r="R15" t="n">
-        <v>6665423</v>
+        <v>6665154</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2238,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,19 +2281,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R16" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131257316</v>
+        <v>131255771</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>81249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488852</v>
+        <v>488818</v>
       </c>
       <c r="R21" t="n">
-        <v>6665209</v>
+        <v>6665110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2910,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131255771</v>
+        <v>131257316</v>
       </c>
       <c r="B22" t="n">
-        <v>81249</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488818</v>
+        <v>488852</v>
       </c>
       <c r="R22" t="n">
-        <v>6665110</v>
+        <v>6665209</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3497,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131257239</v>
+        <v>131255910</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,39 +3508,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488852</v>
+        <v>488763</v>
       </c>
       <c r="R27" t="n">
-        <v>6665286</v>
+        <v>6665157</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,12 +3577,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,7 +3609,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131255910</v>
+        <v>131258531</v>
       </c>
       <c r="B28" t="n">
         <v>79264</v>
@@ -3649,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488763</v>
+        <v>488725</v>
       </c>
       <c r="R28" t="n">
-        <v>6665157</v>
+        <v>6665212</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,12 +3689,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3737,34 +3732,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R29" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131256459</v>
+        <v>131257385</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,39 +4414,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488669</v>
+        <v>488876</v>
       </c>
       <c r="R35" t="n">
-        <v>6665268</v>
+        <v>6665194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4478,7 +4469,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,12 +4479,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Lågstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4520,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131257385</v>
+        <v>131256459</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>57899</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4531,30 +4522,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488876</v>
+        <v>488669</v>
       </c>
       <c r="R36" t="n">
-        <v>6665194</v>
+        <v>6665268</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131260583</v>
+        <v>131257424</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488834</v>
+        <v>488876</v>
       </c>
       <c r="R4" t="n">
-        <v>6665228</v>
+        <v>6665177</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1129,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131257424</v>
+        <v>131256691</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,34 +1135,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488876</v>
+        <v>488667</v>
       </c>
       <c r="R6" t="n">
-        <v>6665177</v>
+        <v>6665262</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131256691</v>
+        <v>131260583</v>
       </c>
       <c r="B7" t="n">
         <v>57902</v>
@@ -1272,7 +1272,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488667</v>
+        <v>488834</v>
       </c>
       <c r="R7" t="n">
-        <v>6665262</v>
+        <v>6665228</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131256423</v>
+        <v>131257188</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,51 +1369,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488671</v>
+        <v>488804</v>
       </c>
       <c r="R8" t="n">
-        <v>6665267</v>
+        <v>6665288</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1434,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131257188</v>
+        <v>131256423</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,33 +1477,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488804</v>
+        <v>488671</v>
       </c>
       <c r="R9" t="n">
-        <v>6665288</v>
+        <v>6665267</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131256730</v>
+        <v>131260641</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,34 +1598,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488689</v>
+        <v>488859</v>
       </c>
       <c r="R10" t="n">
-        <v>6665231</v>
+        <v>6665292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257520</v>
+        <v>131257290</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,34 +1715,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488939</v>
+        <v>488842</v>
       </c>
       <c r="R11" t="n">
-        <v>6665149</v>
+        <v>6665224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131260641</v>
+        <v>131256673</v>
       </c>
       <c r="B12" t="n">
         <v>57902</v>
@@ -1851,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488859</v>
+        <v>488652</v>
       </c>
       <c r="R12" t="n">
-        <v>6665292</v>
+        <v>6665282</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,12 +1906,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257290</v>
+        <v>131257520</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,39 +1949,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488842</v>
+        <v>488939</v>
       </c>
       <c r="R13" t="n">
-        <v>6665224</v>
+        <v>6665149</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256673</v>
+        <v>131256730</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,39 +2061,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488652</v>
+        <v>488689</v>
       </c>
       <c r="R14" t="n">
-        <v>6665282</v>
+        <v>6665231</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131257479</v>
+        <v>131255096</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,19 +2173,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488908</v>
+        <v>488961</v>
       </c>
       <c r="R15" t="n">
-        <v>6665154</v>
+        <v>6665423</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,7 +2274,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131255096</v>
+        <v>131256750</v>
       </c>
       <c r="B16" t="n">
         <v>79264</v>
@@ -2305,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488961</v>
+        <v>488704</v>
       </c>
       <c r="R16" t="n">
-        <v>6665423</v>
+        <v>6665241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2340,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,12 +2354,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131256750</v>
+        <v>131257479</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,23 +2397,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488704</v>
+        <v>488908</v>
       </c>
       <c r="R17" t="n">
-        <v>6665241</v>
+        <v>6665154</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Stambrott. Hängande låga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256401</v>
+        <v>131256403</v>
       </c>
       <c r="B18" t="n">
         <v>79264</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488679</v>
+        <v>488680</v>
       </c>
       <c r="R18" t="n">
-        <v>6665255</v>
+        <v>6665257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256403</v>
+        <v>131256401</v>
       </c>
       <c r="B19" t="n">
         <v>79264</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488680</v>
+        <v>488679</v>
       </c>
       <c r="R19" t="n">
-        <v>6665257</v>
+        <v>6665255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131258531</v>
+        <v>131257239</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3620,34 +3620,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488725</v>
+        <v>488852</v>
       </c>
       <c r="R28" t="n">
-        <v>6665212</v>
+        <v>6665286</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,12 +3694,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131257239</v>
+        <v>131258531</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,39 +3737,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488852</v>
+        <v>488725</v>
       </c>
       <c r="R29" t="n">
-        <v>6665286</v>
+        <v>6665212</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,7 +3838,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131258537</v>
+        <v>131255108</v>
       </c>
       <c r="B30" t="n">
         <v>79264</v>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488726</v>
+        <v>488978</v>
       </c>
       <c r="R30" t="n">
-        <v>6665209</v>
+        <v>6665417</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3950,7 +3950,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131255108</v>
+        <v>131258537</v>
       </c>
       <c r="B31" t="n">
         <v>79264</v>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488978</v>
+        <v>488726</v>
       </c>
       <c r="R31" t="n">
-        <v>6665417</v>
+        <v>6665209</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4179,7 +4179,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131256603</v>
+        <v>131257913</v>
       </c>
       <c r="B33" t="n">
         <v>79264</v>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488625</v>
+        <v>488913</v>
       </c>
       <c r="R33" t="n">
-        <v>6665252</v>
+        <v>6665358</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,7 +4291,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131257913</v>
+        <v>131256603</v>
       </c>
       <c r="B34" t="n">
         <v>79264</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488913</v>
+        <v>488625</v>
       </c>
       <c r="R34" t="n">
-        <v>6665358</v>
+        <v>6665252</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257343</v>
+        <v>131257035</v>
       </c>
       <c r="B40" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,39 +4975,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488872</v>
+        <v>488760</v>
       </c>
       <c r="R40" t="n">
-        <v>6665191</v>
+        <v>6665301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5039,7 +5034,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5049,12 +5044,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131257035</v>
+        <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5092,34 +5087,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488760</v>
+        <v>488872</v>
       </c>
       <c r="R41" t="n">
-        <v>6665301</v>
+        <v>6665191</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Mycket barkfläk, hagelsalvor på många träd, skalade klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,7 +5193,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131273946</v>
+        <v>131273991</v>
       </c>
       <c r="B42" t="n">
         <v>79264</v>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488774</v>
+        <v>488928</v>
       </c>
       <c r="R42" t="n">
-        <v>6665353</v>
+        <v>6665146</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273991</v>
+        <v>131273946</v>
       </c>
       <c r="B43" t="n">
         <v>79264</v>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488928</v>
+        <v>488774</v>
       </c>
       <c r="R43" t="n">
-        <v>6665146</v>
+        <v>6665353</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>

--- a/artfynd/A 32054-2021 artfynd.xlsx
+++ b/artfynd/A 32054-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131257487</v>
+        <v>131255771</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488926</v>
+        <v>488818</v>
       </c>
       <c r="R2" t="n">
-        <v>6665146</v>
+        <v>6665110</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131257646</v>
+        <v>131255096</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488914</v>
+        <v>488961</v>
       </c>
       <c r="R3" t="n">
-        <v>6665193</v>
+        <v>6665423</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131257424</v>
+        <v>131255108</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488876</v>
+        <v>488978</v>
       </c>
       <c r="R4" t="n">
-        <v>6665177</v>
+        <v>6665417</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,30 +1006,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131255793</v>
+        <v>131255910</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488817</v>
+        <v>488763</v>
       </c>
       <c r="R5" t="n">
-        <v>6665110</v>
+        <v>6665157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar.</t>
+          <t>Tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,50 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131256691</v>
+        <v>131256338</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488667</v>
+        <v>488693</v>
       </c>
       <c r="R6" t="n">
-        <v>6665262</v>
+        <v>6665189</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,50 +1230,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131260583</v>
+        <v>131256343</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488834</v>
+        <v>488691</v>
       </c>
       <c r="R7" t="n">
-        <v>6665228</v>
+        <v>6665194</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran. Flera träd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,30 +1342,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131257188</v>
+        <v>131256401</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488804</v>
+        <v>488679</v>
       </c>
       <c r="R8" t="n">
-        <v>6665288</v>
+        <v>6665255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,62 +1454,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131256423</v>
+        <v>131256403</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488671</v>
+        <v>488680</v>
       </c>
       <c r="R9" t="n">
-        <v>6665267</v>
+        <v>6665257</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1534,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,50 +1566,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131260641</v>
+        <v>131256603</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488859</v>
+        <v>488625</v>
       </c>
       <c r="R10" t="n">
-        <v>6665292</v>
+        <v>6665252</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1646,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,50 +1678,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131257290</v>
+        <v>131256649</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488842</v>
+        <v>488685</v>
       </c>
       <c r="R11" t="n">
-        <v>6665224</v>
+        <v>6665288</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,50 +1790,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131256673</v>
+        <v>131256730</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488652</v>
+        <v>488689</v>
       </c>
       <c r="R12" t="n">
-        <v>6665282</v>
+        <v>6665231</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,14 +1902,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131257520</v>
+        <v>131256750</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1973,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488939</v>
+        <v>488704</v>
       </c>
       <c r="R13" t="n">
-        <v>6665149</v>
+        <v>6665241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2050,14 +2014,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131256730</v>
+        <v>131257035</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2085,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488689</v>
+        <v>488760</v>
       </c>
       <c r="R14" t="n">
-        <v>6665231</v>
+        <v>6665301</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2094,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,14 +2126,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131255096</v>
+        <v>131257045</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2197,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488961</v>
+        <v>488760</v>
       </c>
       <c r="R15" t="n">
-        <v>6665423</v>
+        <v>6665302</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2274,14 +2238,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131256750</v>
+        <v>131257316</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2309,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488704</v>
+        <v>488852</v>
       </c>
       <c r="R16" t="n">
-        <v>6665241</v>
+        <v>6665209</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2344,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2386,30 +2350,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131257479</v>
+        <v>131257424</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2417,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488908</v>
+        <v>488876</v>
       </c>
       <c r="R17" t="n">
-        <v>6665154</v>
+        <v>6665177</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,12 +2430,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Stambrott. Hängande låga.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,14 +2462,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131256403</v>
+        <v>131257440</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2529,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488680</v>
+        <v>488885</v>
       </c>
       <c r="R18" t="n">
-        <v>6665257</v>
+        <v>6665181</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2542,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2606,14 +2574,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131256401</v>
+        <v>131257520</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2641,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488679</v>
+        <v>488939</v>
       </c>
       <c r="R19" t="n">
-        <v>6665255</v>
+        <v>6665149</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2718,14 +2686,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131257637</v>
+        <v>131257544</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2753,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488909</v>
+        <v>488940</v>
       </c>
       <c r="R20" t="n">
-        <v>6665191</v>
+        <v>6665149</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2830,32 +2798,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131255771</v>
+        <v>131257637</v>
       </c>
       <c r="B21" t="n">
-        <v>81249</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2865,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488818</v>
+        <v>488909</v>
       </c>
       <c r="R21" t="n">
-        <v>6665110</v>
+        <v>6665191</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,7 +2868,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,7 +2878,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,14 +2910,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131257316</v>
+        <v>131257642</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2972,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488852</v>
+        <v>488913</v>
       </c>
       <c r="R22" t="n">
-        <v>6665209</v>
+        <v>6665191</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3049,14 +3022,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131257642</v>
+        <v>131257646</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3084,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488913</v>
+        <v>488914</v>
       </c>
       <c r="R23" t="n">
-        <v>6665191</v>
+        <v>6665193</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3119,7 +3092,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3102,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3161,14 +3134,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131257045</v>
+        <v>131257650</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3196,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488760</v>
+        <v>488911</v>
       </c>
       <c r="R24" t="n">
-        <v>6665302</v>
+        <v>6665227</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,12 +3214,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,14 +3246,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131257650</v>
+        <v>131257731</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3308,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488911</v>
+        <v>488874</v>
       </c>
       <c r="R25" t="n">
-        <v>6665227</v>
+        <v>6665272</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3343,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,7 +3326,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3385,14 +3358,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131257544</v>
+        <v>131257913</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3420,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488940</v>
+        <v>488913</v>
       </c>
       <c r="R26" t="n">
-        <v>6665149</v>
+        <v>6665358</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3455,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3497,14 +3470,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131255910</v>
+        <v>131258531</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3532,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488763</v>
+        <v>488725</v>
       </c>
       <c r="R27" t="n">
-        <v>6665157</v>
+        <v>6665212</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3567,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,12 +3550,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,50 +3582,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131257239</v>
+        <v>131258537</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488852</v>
+        <v>488726</v>
       </c>
       <c r="R28" t="n">
-        <v>6665286</v>
+        <v>6665209</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,7 +3652,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,12 +3662,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Barkfläk, hagelsalva.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,14 +3694,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131258531</v>
+        <v>131260531</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3761,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488725</v>
+        <v>488786</v>
       </c>
       <c r="R29" t="n">
-        <v>6665212</v>
+        <v>6665188</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3796,7 +3764,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3774,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3838,14 +3806,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131255108</v>
+        <v>131273940</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3867,19 +3835,22 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488978</v>
+        <v>488785</v>
       </c>
       <c r="R30" t="n">
-        <v>6665417</v>
+        <v>6665325</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3906,58 +3877,44 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131258537</v>
+        <v>131273946</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3979,19 +3936,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488726</v>
+        <v>488774</v>
       </c>
       <c r="R31" t="n">
-        <v>6665209</v>
+        <v>6665353</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4018,97 +3978,81 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131257659</v>
+        <v>131273991</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hyttfallet, Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488901</v>
+        <v>488928</v>
       </c>
       <c r="R32" t="n">
-        <v>6665222</v>
+        <v>6665146</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4135,92 +4079,92 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131257913</v>
+        <v>131256423</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488913</v>
+        <v>488671</v>
       </c>
       <c r="R33" t="n">
-        <v>6665358</v>
+        <v>6665267</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4249,7 +4193,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4259,12 +4203,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,45 +4230,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131256603</v>
+        <v>131256459</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488625</v>
+        <v>488669</v>
       </c>
       <c r="R34" t="n">
-        <v>6665252</v>
+        <v>6665268</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,7 +4305,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4371,12 +4315,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Färska och äldre hack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4347,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131257385</v>
+        <v>131256256</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,30 +4358,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488876</v>
+        <v>488691</v>
       </c>
       <c r="R35" t="n">
-        <v>6665194</v>
+        <v>6665177</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4469,7 +4422,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,12 +4432,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lågstubbe.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4464,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131256459</v>
+        <v>131256516</v>
       </c>
       <c r="B36" t="n">
-        <v>57899</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,16 +4475,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4551,10 +4504,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488669</v>
+        <v>488625</v>
       </c>
       <c r="R36" t="n">
-        <v>6665268</v>
+        <v>6665252</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,12 +4549,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre hack.</t>
+          <t>Rikligt hackad. Tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4581,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131260531</v>
+        <v>131256673</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4639,34 +4592,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488786</v>
+        <v>488652</v>
       </c>
       <c r="R37" t="n">
-        <v>6665188</v>
+        <v>6665282</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,12 +4666,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4740,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131257731</v>
+        <v>131256691</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4751,34 +4709,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488874</v>
+        <v>488667</v>
       </c>
       <c r="R38" t="n">
-        <v>6665272</v>
+        <v>6665262</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4810,7 +4773,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,12 +4783,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,10 +4815,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131257440</v>
+        <v>131257239</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4863,34 +4826,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488885</v>
+        <v>488852</v>
       </c>
       <c r="R39" t="n">
-        <v>6665181</v>
+        <v>6665286</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4922,7 +4890,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4932,12 +4900,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Barkfläk, hagelsalva.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4964,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131257035</v>
+        <v>131257290</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,34 +4943,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488760</v>
+        <v>488842</v>
       </c>
       <c r="R40" t="n">
-        <v>6665301</v>
+        <v>6665224</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5034,7 +5007,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5044,12 +5017,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5079,7 +5052,7 @@
         <v>131257343</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131273991</v>
+        <v>131257487</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5204,40 +5177,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488928</v>
+        <v>488926</v>
       </c>
       <c r="R42" t="n">
         <v>6665146</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5264,40 +5239,54 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273946</v>
+        <v>131257659</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5305,40 +5294,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488774</v>
+        <v>488901</v>
       </c>
       <c r="R43" t="n">
-        <v>6665353</v>
+        <v>6665222</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5365,40 +5356,54 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131256516</v>
+        <v>131260583</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488625</v>
+        <v>488834</v>
       </c>
       <c r="R44" t="n">
-        <v>6665252</v>
+        <v>6665228</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5470,7 +5475,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5480,12 +5485,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt hackad. Tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5512,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131273940</v>
+        <v>131260641</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5523,40 +5528,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hyttfallet, Dlr</t>
+          <t>Hyttfallet, Hyttfallet, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488785</v>
+        <v>488859</v>
       </c>
       <c r="R45" t="n">
-        <v>6665325</v>
+        <v>6665292</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5583,33 +5590,157 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131267934</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hyttfallet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>488711</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6665178</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett fåtal korta hackrader på äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
